--- a/Data/Building/Lab.Temperature.xlsx
+++ b/Data/Building/Lab.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709235943</v>
+        <v>1711828974</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709261032</v>
+        <v>1711853197</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709264763</v>
+        <v>1711856669</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709226691</v>
+        <v>1711863327</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,15 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709233932</v>
+        <v>1711877081</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +638,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709244032</v>
+        <v>1711907567</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709262776</v>
+        <v>1711917182</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709272029</v>
+        <v>1711932361</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +741,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709315278</v>
+        <v>1711935887</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +770,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709325903</v>
+        <v>1711940959</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +803,15 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709341183</v>
+        <v>1711951552</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +840,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709344882</v>
+        <v>1711990942</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +877,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709352427</v>
+        <v>1711997905</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709395276</v>
+        <v>1712007156</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +939,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709401348</v>
+        <v>1712023579</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +980,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +999,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709410679</v>
+        <v>1712027073</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1009,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1032,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709429155</v>
+        <v>1712079468</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1046,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709435713</v>
+        <v>1712088809</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1075,15 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1102,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709492771</v>
+        <v>1712107131</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1116,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1135,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709501926</v>
+        <v>1712110718</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1145,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1168,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709515363</v>
+        <v>1712118493</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1178,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1201,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709519418</v>
+        <v>1712160127</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1215,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1234,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709572468</v>
+        <v>1712166973</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1248,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1267,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709581631</v>
+        <v>1712176548</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1281,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1304,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709601334</v>
+        <v>1712193576</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1318,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1337,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709605290</v>
+        <v>1712200676</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1351,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1370,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709611972</v>
+        <v>1712208806</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1384,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1403,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709625406</v>
+        <v>1712216755</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1417,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1436,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709661574</v>
+        <v>1712254779</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1450,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1469,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709671742</v>
+        <v>1712264208</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1483,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1506,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709690248</v>
+        <v>1712279098</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1520,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1539,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709699021</v>
+        <v>1712282574</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1553,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1572,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709709123</v>
+        <v>1712337699</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1582,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1605,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709719253</v>
+        <v>1712346893</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1615,15 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1642,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709750257</v>
+        <v>1712368136</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1656,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1675,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709760505</v>
+        <v>1712376624</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1685,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1708,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709781661</v>
+        <v>1712385912</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1718,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1741,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709791951</v>
+        <v>1712398602</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1755,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1774,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709833234</v>
+        <v>1712425821</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1788,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1807,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709843257</v>
+        <v>1712435208</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1821,11 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1844,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709860998</v>
+        <v>1712456537</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1858,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1877,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709861881</v>
+        <v>1712464894</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1887,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1910,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709865691</v>
+        <v>1712474092</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1920,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1943,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709866726</v>
+        <v>1712485896</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1953,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1976,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709869130</v>
+        <v>1712512513</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1990,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2009,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709870060</v>
+        <v>1712521696</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2023,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2046,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709872899</v>
+        <v>1712541574</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2060,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2079,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709932888</v>
+        <v>1712542395</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2093,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2116,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709945144</v>
+        <v>1712546629</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2130,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2149,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709949140</v>
+        <v>1712547576</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2159,15 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2186,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709954074</v>
+        <v>1712549447</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2196,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2219,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710000384</v>
+        <v>1712550580</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2229,15 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2256,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710007155</v>
+        <v>1712553173</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2270,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2289,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710016834</v>
+        <v>1712554027</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2303,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2326,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710033033</v>
+        <v>1712558168</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2340,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2359,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710036865</v>
+        <v>1712606726</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2369,15 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2396,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710044499</v>
+        <v>1712625394</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2406,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2429,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710086865</v>
+        <v>1712628990</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2443,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2462,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710093685</v>
+        <v>1712634497</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2472,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2495,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710103181</v>
+        <v>1712678667</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2505,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2528,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710120031</v>
+        <v>1712687738</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2542,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2561,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710123496</v>
+        <v>1712697309</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2571,15 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2598,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710131440</v>
+        <v>1712720827</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2608,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2631,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710145527</v>
+        <v>1712724326</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2645,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2664,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710179177</v>
+        <v>1712770939</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2678,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2697,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710188757</v>
+        <v>1712779970</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2711,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2734,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710205448</v>
+        <v>1712799312</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2748,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2767,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710209174</v>
+        <v>1712800124</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2777,15 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2804,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710215881</v>
+        <v>1712801832</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2814,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2837,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710259748</v>
+        <v>1712802901</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2847,15 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2874,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710266220</v>
+        <v>1712804645</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2888,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2907,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710275728</v>
+        <v>1712805702</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2921,11 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2944,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710293616</v>
+        <v>1712806784</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2958,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2977,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710301885</v>
+        <v>1712808944</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2987,15 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3014,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710311101</v>
+        <v>1712809618</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +3024,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3047,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710323419</v>
+        <v>1712814393</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3061,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3080,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710353557</v>
+        <v>1712856851</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3094,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3113,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710362813</v>
+        <v>1712866000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3127,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3150,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710387143</v>
+        <v>1712887396</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3164,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3183,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710396935</v>
+        <v>1712893237</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3197,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3216,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710437685</v>
+        <v>1712946374</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3230,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3249,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710446818</v>
+        <v>1712955889</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3263,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3286,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710464247</v>
+        <v>1712972103</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3300,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3319,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710468121</v>
+        <v>1712980256</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3333,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3352,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710473831</v>
+        <v>1712989451</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3366,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3385,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710486574</v>
+        <v>1712999763</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3399,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3418,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710524509</v>
+        <v>1713030588</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3432,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3451,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710534227</v>
+        <v>1713039991</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3465,11 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3488,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710551476</v>
+        <v>1713060619</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3502,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3521,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710558352</v>
+        <v>1713069106</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3535,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3554,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710614031</v>
+        <v>1713078590</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3564,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3587,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710623392</v>
+        <v>1713088581</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3597,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3620,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710638836</v>
+        <v>1713118465</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3634,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3653,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710639774</v>
+        <v>1713128073</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3667,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3690,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710641598</v>
+        <v>1713143781</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3704,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3723,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710642578</v>
+        <v>1713147485</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3733,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3756,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710644419</v>
+        <v>1713202305</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3770,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3789,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710645346</v>
+        <v>1713211842</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3803,11 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3826,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710646610</v>
+        <v>1713227519</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3840,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3859,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710648035</v>
+        <v>1713231398</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3869,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3892,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710649280</v>
+        <v>1713237840</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3902,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3925,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710650859</v>
+        <v>1713239668</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3935,15 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3962,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710651907</v>
+        <v>1713244363</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3972,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3995,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710653339</v>
+        <v>1713283890</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +4005,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4028,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710657032</v>
+        <v>1713290507</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4042,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4061,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710707510</v>
+        <v>1713299860</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4075,11 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4098,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710723597</v>
+        <v>1713315468</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4112,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4131,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710724549</v>
+        <v>1713319226</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4141,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4164,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710726406</v>
+        <v>1713323979</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3953,10 +4174,11 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4197,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710727408</v>
+        <v>1713334011</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4207,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4230,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710729126</v>
+        <v>1713378045</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4244,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4263,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710730446</v>
+        <v>1713387825</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4277,11 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4300,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710731648</v>
+        <v>1713401620</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4314,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4333,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710733211</v>
+        <v>1713405371</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4343,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4366,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710734476</v>
+        <v>1713410268</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4376,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4399,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710735939</v>
+        <v>1713411496</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4409,15 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4436,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710737056</v>
+        <v>1713412415</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4446,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4469,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710738259</v>
+        <v>1713414256</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4479,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4502,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710740449</v>
+        <v>1713461405</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4516,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4535,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710792965</v>
+        <v>1713470409</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4549,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4572,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710810390</v>
+        <v>1713488392</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4586,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4605,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710814251</v>
+        <v>1713491873</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4619,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4638,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710820609</v>
+        <v>1713496370</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4652,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4671,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710833311</v>
+        <v>1713545946</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4685,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4704,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710873586</v>
+        <v>1713551287</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4718,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4737,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710895988</v>
+        <v>1713560857</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4747,15 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4774,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710901229</v>
+        <v>1713577332</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4784,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4807,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710910334</v>
+        <v>1713584680</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4817,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyHot</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4840,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710929201</v>
+        <v>1713638725</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4850,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4873,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710957306</v>
+        <v>1713648248</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4883,15 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4910,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710966936</v>
+        <v>1713663022</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4924,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4943,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710986996</v>
+        <v>1713671396</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4957,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4976,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710995372</v>
+        <v>1713716813</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4986,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +5009,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711004795</v>
+        <v>1713726075</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +5019,15 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyHot</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5046,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711016612</v>
+        <v>1713746197</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +5056,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5079,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711045677</v>
+        <v>1713749836</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5093,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5112,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711055196</v>
+        <v>1713755746</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +5122,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5145,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711071557</v>
+        <v>1713769395</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5159,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5178,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711076290</v>
+        <v>1713809430</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5188,11 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5211,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711129313</v>
+        <v>1713818464</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5221,15 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5248,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711138617</v>
+        <v>1713836849</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5262,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5281,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711157413</v>
+        <v>1713840518</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5295,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5314,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711164021</v>
+        <v>1713893389</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5324,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5347,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711172030</v>
+        <v>1713902392</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5357,15 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyHot</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5384,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711180856</v>
+        <v>1713923051</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5394,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5417,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711216303</v>
+        <v>1713928618</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5431,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5450,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711226282</v>
+        <v>1713932189</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5460,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5483,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711243650</v>
+        <v>1713974750</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5497,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5516,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711256355</v>
+        <v>1713983176</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5526,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5549,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711296237</v>
+        <v>1713992569</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5559,15 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5586,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711303472</v>
+        <v>1714009362</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5600,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5619,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711313052</v>
+        <v>1714012873</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5629,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: ExcessivelyCold</t>
+          <t>Lab.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5652,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711327793</v>
+        <v>1714014994</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5662,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Cold</t>
+          <t>Lab.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5685,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711331658</v>
+        <v>1714015971</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5695,15 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5722,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711338548</v>
+        <v>1714019854</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5736,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5755,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711382504</v>
+        <v>1714063416</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5769,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5788,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711389173</v>
+        <v>1714070990</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5802,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5821,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711398722</v>
+        <v>1714080792</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5835,11 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5858,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711415201</v>
+        <v>1714096825</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5872,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5891,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711418956</v>
+        <v>1714097781</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5901,15 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5928,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711425380</v>
+        <v>1714099403</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5938,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Warm</t>
+          <t>Lab.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5961,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711468802</v>
+        <v>1714100384</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5971,15 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lab.Temperature.state: Comfortable</t>
+          <t>Lab.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5998,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711475845</v>
+        <v>1714101934</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +6012,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +6031,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711485004</v>
+        <v>1714160679</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +6045,11 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6068,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711505681</v>
+        <v>1714181976</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +6082,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6101,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711513870</v>
+        <v>1714189337</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6115,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6134,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711523133</v>
+        <v>1714198611</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6148,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6167,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711555380</v>
+        <v>1714233796</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6181,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6200,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711562444</v>
+        <v>1714240115</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6214,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6233,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711571712</v>
+        <v>1714249585</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6247,11 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6270,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711592636</v>
+        <v>1714268064</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6284,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6303,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711601389</v>
+        <v>1714275995</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6317,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6336,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711610644</v>
+        <v>1714284720</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6350,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6369,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711621295</v>
+        <v>1714293408</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6383,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
